--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="184">
   <si>
     <t>Datum</t>
   </si>
@@ -105,21 +105,51 @@
     <t>Pondělí</t>
   </si>
   <si>
+    <t>05.05.2026</t>
+  </si>
+  <si>
+    <t>Úterý</t>
+  </si>
+  <si>
+    <t>06.05.2026</t>
+  </si>
+  <si>
+    <t>Středa</t>
+  </si>
+  <si>
+    <t>07.05.2026</t>
+  </si>
+  <si>
+    <t>Čtvrtek</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>08.05.2026</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>09.05.2026</t>
+  </si>
+  <si>
+    <t>10.05.2026</t>
+  </si>
+  <si>
+    <t>11.05.2026</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
-    <t>Středa</t>
-  </si>
-  <si>
     <t>02.04.2026</t>
   </si>
   <si>
-    <t>Čtvrtek</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
     <t>03.04.2026</t>
   </si>
   <si>
@@ -135,9 +165,6 @@
     <t>07.04.2026</t>
   </si>
   <si>
-    <t>Úterý</t>
-  </si>
-  <si>
     <t>Chlubna Tomáš</t>
   </si>
   <si>
@@ -172,12 +199,6 @@
   </si>
   <si>
     <t>13.04.2026</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>09:00</t>
   </si>
   <si>
     <t>14.04.2026</t>
@@ -1060,6 +1081,343 @@
         <v>40132.0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="3">
+        <v>40068.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="3">
+        <v>40068.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="3">
+        <v>40132.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="3">
+        <v>40148.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="3">
+        <v>40004.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="3">
+        <v>40004.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H32" s="3">
+        <v>40660.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1109,10 +1467,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>13</v>
@@ -1129,10 +1487,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>17</v>
@@ -1149,10 +1507,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
@@ -1169,10 +1527,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H5" s="3">
         <v>40004.0</v>
@@ -1180,10 +1538,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>13</v>
@@ -1200,10 +1558,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
@@ -1220,10 +1578,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
@@ -1240,10 +1598,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>21</v>
@@ -1252,7 +1610,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>16</v>
@@ -1260,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H10" s="3">
         <v>40132.0</v>
@@ -1271,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -1291,7 +1649,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
@@ -1311,7 +1669,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -1331,7 +1689,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -1342,7 +1700,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>20</v>
@@ -1362,7 +1720,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>20</v>
@@ -1373,7 +1731,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>26</v>
@@ -1384,7 +1742,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>28</v>
@@ -1404,7 +1762,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>28</v>
@@ -1424,7 +1782,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>28</v>
@@ -1444,7 +1802,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>28</v>
@@ -1455,10 +1813,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>13</v>
@@ -1475,10 +1833,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>17</v>
@@ -1495,10 +1853,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>18</v>
@@ -1515,50 +1873,50 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H27" s="3">
         <v>40951.75</v>
@@ -1566,10 +1924,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>13</v>
@@ -1586,10 +1944,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>17</v>
@@ -1606,10 +1964,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>18</v>
@@ -1626,10 +1984,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H31" s="3">
         <v>40644.0</v>
@@ -1637,10 +1995,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>13</v>
@@ -1657,10 +2015,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>17</v>
@@ -1677,10 +2035,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>18</v>
@@ -1697,10 +2055,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>21</v>
@@ -1709,7 +2067,7 @@
         <v>22</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>16</v>
@@ -1717,10 +2075,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H36" s="3">
         <v>41040.0</v>
@@ -1728,7 +2086,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>12</v>
@@ -1740,15 +2098,15 @@
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>12</v>
@@ -1760,15 +2118,15 @@
         <v>14</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>12</v>
@@ -1780,15 +2138,15 @@
         <v>14</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>12</v>
@@ -1799,7 +2157,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>20</v>
@@ -1819,7 +2177,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>20</v>
@@ -1830,7 +2188,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>26</v>
@@ -1841,7 +2199,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>28</v>
@@ -1853,15 +2211,15 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>28</v>
@@ -1873,15 +2231,15 @@
         <v>14</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>28</v>
@@ -1892,10 +2250,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>13</v>
@@ -1912,10 +2270,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>18</v>
@@ -1932,19 +2290,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -1952,19 +2310,19 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>14</v>
@@ -1972,10 +2330,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H51" s="3">
         <v>41570.0</v>
@@ -1983,10 +2341,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>17</v>
@@ -2003,10 +2361,10 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>18</v>
@@ -2023,10 +2381,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>13</v>
@@ -2043,10 +2401,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H55" s="3">
         <v>41148.0</v>
@@ -2054,10 +2412,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>13</v>
@@ -2074,10 +2432,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>17</v>
@@ -2094,10 +2452,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>18</v>
@@ -2114,10 +2472,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>21</v>
@@ -2126,7 +2484,7 @@
         <v>22</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>16</v>
@@ -2134,10 +2492,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H60" s="3">
         <v>41856.0</v>
@@ -2145,7 +2503,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>12</v>
@@ -2165,7 +2523,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>12</v>
@@ -2185,7 +2543,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>12</v>
@@ -2196,7 +2554,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>20</v>
@@ -2216,7 +2574,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>20</v>
@@ -2227,7 +2585,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>26</v>
@@ -2238,7 +2596,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>28</v>
@@ -2258,7 +2616,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>28</v>
@@ -2278,7 +2636,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>28</v>
@@ -2289,10 +2647,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>13</v>
@@ -2309,10 +2667,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>17</v>
@@ -2329,19 +2687,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>14</v>
@@ -2349,30 +2707,30 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H74" s="3">
         <v>42123.5</v>
@@ -2380,10 +2738,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>13</v>
@@ -2400,10 +2758,10 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>17</v>
@@ -2420,10 +2778,10 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H77" s="3">
         <v>40828.0</v>
@@ -2431,10 +2789,10 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>13</v>
@@ -2451,10 +2809,10 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>17</v>
@@ -2471,10 +2829,10 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>21</v>
@@ -2483,7 +2841,7 @@
         <v>22</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>16</v>
@@ -2491,10 +2849,10 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H81" s="3">
         <v>40004.0</v>
@@ -2502,7 +2860,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -2514,15 +2872,15 @@
         <v>14</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
@@ -2534,15 +2892,15 @@
         <v>14</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>12</v>
@@ -2553,7 +2911,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>20</v>
@@ -2573,7 +2931,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>20</v>
@@ -2584,7 +2942,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>26</v>
@@ -2595,7 +2953,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -2615,7 +2973,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -2635,7 +2993,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>28</v>
@@ -2646,10 +3004,10 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>13</v>
@@ -2666,10 +3024,10 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>18</v>
@@ -2686,50 +3044,50 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H95" s="3">
         <v>42437.0</v>
@@ -2737,10 +3095,10 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>13</v>
@@ -2757,10 +3115,10 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>17</v>
@@ -2777,10 +3135,10 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H98" s="3">
         <v>41088.0</v>
@@ -2788,10 +3146,10 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>13</v>
@@ -2808,10 +3166,10 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>17</v>
@@ -2828,10 +3186,10 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>18</v>
@@ -2848,10 +3206,10 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>21</v>
@@ -2860,7 +3218,7 @@
         <v>22</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>16</v>
@@ -2868,10 +3226,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H103" s="3">
         <v>43072.0</v>
@@ -2926,7 +3284,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -2935,12 +3293,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>26</v>
@@ -2951,7 +3309,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -2971,7 +3329,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -2991,7 +3349,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>28</v>
@@ -3011,7 +3369,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -3022,10 +3380,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
@@ -3042,10 +3400,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
@@ -3062,10 +3420,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -3074,18 +3432,18 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>21</v>
@@ -3102,10 +3460,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H12" s="3">
         <v>40248.0</v>
@@ -3113,10 +3471,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>13</v>
@@ -3133,10 +3491,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>17</v>
@@ -3153,10 +3511,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>18</v>
@@ -3173,10 +3531,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H16" s="3">
         <v>40220.0</v>
@@ -3184,10 +3542,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>13</v>
@@ -3204,10 +3562,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>17</v>
@@ -3216,18 +3574,18 @@
         <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>18</v>
@@ -3236,18 +3594,18 @@
         <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>21</v>
@@ -3256,7 +3614,7 @@
         <v>22</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>16</v>
@@ -3264,10 +3622,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3277,15 +3635,15 @@
         <v>40483.5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -3319,7 +3677,7 @@
         <v>0.0</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="AI22" s="3">
         <v>0.0</v>
@@ -3366,7 +3724,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>12</v>
@@ -3386,7 +3744,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>12</v>
@@ -3406,7 +3764,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>12</v>
@@ -3426,7 +3784,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>12</v>
@@ -3437,7 +3795,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>20</v>
@@ -3457,7 +3815,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>20</v>
@@ -3466,12 +3824,12 @@
         <v>17</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>20</v>
@@ -3482,7 +3840,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>26</v>
@@ -3491,12 +3849,12 @@
         <v>17</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>26</v>
@@ -3507,7 +3865,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
@@ -3527,7 +3885,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>28</v>
@@ -3547,7 +3905,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>28</v>
@@ -3567,7 +3925,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>28</v>
@@ -3578,10 +3936,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>18</v>
@@ -3598,10 +3956,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>17</v>
@@ -3610,18 +3968,18 @@
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>21</v>
@@ -3638,10 +3996,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>13</v>
@@ -3658,10 +4016,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -3671,15 +4029,15 @@
         <v>41160.0</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -3713,7 +4071,7 @@
         <v>0.0</v>
       </c>
       <c r="AD41" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="AI41" s="3">
         <v>0.0</v>
@@ -3760,10 +4118,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>13</v>
@@ -3780,10 +4138,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>17</v>
@@ -3800,10 +4158,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>18</v>
@@ -3820,10 +4178,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H45" s="3">
         <v>40820.0</v>
@@ -3831,10 +4189,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>13</v>
@@ -3851,10 +4209,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>17</v>
@@ -3863,18 +4221,18 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>18</v>
@@ -3883,18 +4241,18 @@
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>21</v>
@@ -3903,7 +4261,7 @@
         <v>22</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>16</v>
@@ -3911,10 +4269,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3924,15 +4282,15 @@
         <v>41286.0</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -3966,7 +4324,7 @@
         <v>0.0</v>
       </c>
       <c r="AD51" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="AI51" s="3">
         <v>0.0</v>
@@ -4013,7 +4371,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>12</v>
@@ -4033,7 +4391,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>12</v>
@@ -4053,7 +4411,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>12</v>
@@ -4073,7 +4431,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -4084,7 +4442,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>20</v>
@@ -4104,7 +4462,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>20</v>
@@ -4113,12 +4471,12 @@
         <v>17</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>20</v>
@@ -4129,7 +4487,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>26</v>
@@ -4138,12 +4496,12 @@
         <v>17</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>26</v>
@@ -4154,7 +4512,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>28</v>
@@ -4174,7 +4532,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>28</v>
@@ -4194,7 +4552,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>28</v>
@@ -4214,7 +4572,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -4225,10 +4583,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>13</v>
@@ -4245,10 +4603,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>17</v>
@@ -4265,10 +4623,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>18</v>
@@ -4285,10 +4643,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>21</v>
@@ -4305,10 +4663,10 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H69" s="3">
         <v>42396.0</v>
@@ -4316,10 +4674,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>13</v>
@@ -4336,10 +4694,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>17</v>
@@ -4348,18 +4706,18 @@
         <v>14</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>18</v>
@@ -4368,18 +4726,18 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -4389,15 +4747,15 @@
         <v>41264.0</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -4431,7 +4789,7 @@
         <v>0.0</v>
       </c>
       <c r="AD74" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="AI74" s="3">
         <v>0.0</v>
@@ -4478,10 +4836,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>13</v>
@@ -4498,10 +4856,10 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>17</v>
@@ -4518,10 +4876,10 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>21</v>
@@ -4530,7 +4888,7 @@
         <v>22</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>16</v>
@@ -4538,10 +4896,10 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H78" s="3">
         <v>41616.0</v>
@@ -4549,7 +4907,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>12</v>
@@ -4569,7 +4927,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>12</v>
@@ -4589,7 +4947,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>12</v>
@@ -4609,7 +4967,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -4620,7 +4978,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>20</v>
@@ -4640,7 +4998,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>20</v>
@@ -4649,12 +5007,12 @@
         <v>17</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>20</v>
@@ -4665,7 +5023,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>26</v>
@@ -4674,12 +5032,12 @@
         <v>17</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>26</v>
@@ -4690,7 +5048,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -4710,7 +5068,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -4730,7 +5088,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>28</v>
@@ -4741,10 +5099,10 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>13</v>
@@ -4761,24 +5119,24 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>18</v>
@@ -4795,10 +5153,10 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>21</v>
@@ -4815,10 +5173,10 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H95" s="3">
         <v>42288.0</v>
@@ -4826,10 +5184,10 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>13</v>
@@ -4846,10 +5204,10 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>17</v>
@@ -4866,10 +5224,10 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>18</v>
@@ -4886,10 +5244,10 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H99" s="3">
         <v>41876.0</v>
@@ -4897,10 +5255,10 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>13</v>
@@ -4917,10 +5275,10 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>17</v>
@@ -4937,10 +5295,10 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>18</v>
@@ -4957,10 +5315,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>21</v>
@@ -4969,7 +5327,7 @@
         <v>22</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>16</v>
@@ -4977,10 +5335,10 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H104" s="3">
         <v>43076.0</v>
@@ -4988,7 +5346,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>12</v>
@@ -5008,7 +5366,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>12</v>
@@ -5028,7 +5386,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>12</v>
@@ -5048,7 +5406,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>12</v>
@@ -5059,7 +5417,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>20</v>
@@ -5079,7 +5437,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>20</v>
@@ -5088,12 +5446,12 @@
         <v>17</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>20</v>
@@ -5104,7 +5462,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>26</v>
@@ -5113,12 +5471,12 @@
         <v>17</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>26</v>
@@ -5129,7 +5487,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>28</v>
@@ -5149,7 +5507,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>28</v>
@@ -5169,7 +5527,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>28</v>
@@ -5189,7 +5547,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>28</v>
@@ -5200,10 +5558,10 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>13</v>
@@ -5220,10 +5578,10 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>17</v>
@@ -5240,10 +5598,10 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>18</v>
@@ -5260,19 +5618,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>14</v>
@@ -5280,16 +5638,16 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>23</v>
@@ -5300,10 +5658,10 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H123" s="3">
         <v>44502.0</v>
@@ -5358,7 +5716,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -5367,12 +5725,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>26</v>
@@ -5383,7 +5741,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -5403,7 +5761,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -5423,7 +5781,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>28</v>
@@ -5443,7 +5801,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -5454,10 +5812,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
@@ -5466,18 +5824,18 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
@@ -5486,18 +5844,18 @@
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -5506,18 +5864,18 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>21</v>
@@ -5534,10 +5892,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H12" s="3">
         <v>40264.0</v>
@@ -5545,10 +5903,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>13</v>
@@ -5557,18 +5915,18 @@
         <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>17</v>
@@ -5577,18 +5935,18 @@
         <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H15" s="3">
         <v>40134.5</v>
@@ -5596,10 +5954,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>13</v>
@@ -5608,18 +5966,18 @@
         <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>17</v>
@@ -5628,18 +5986,18 @@
         <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>21</v>
@@ -5648,7 +6006,7 @@
         <v>22</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>16</v>
@@ -5656,10 +6014,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H19" s="3">
         <v>40415.5</v>
@@ -5667,7 +6025,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -5687,7 +6045,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>12</v>
@@ -5707,7 +6065,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>12</v>
@@ -5727,7 +6085,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>12</v>
@@ -5738,7 +6096,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>20</v>
@@ -5758,7 +6116,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>20</v>
@@ -5767,12 +6125,12 @@
         <v>17</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>20</v>
@@ -5783,7 +6141,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>26</v>
@@ -5792,12 +6150,12 @@
         <v>17</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>26</v>
@@ -5808,7 +6166,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
@@ -5828,7 +6186,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -5848,7 +6206,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -5868,7 +6226,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
@@ -5879,10 +6237,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>13</v>
@@ -5891,18 +6249,18 @@
         <v>14</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>17</v>
@@ -5911,18 +6269,18 @@
         <v>14</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>18</v>
@@ -5931,18 +6289,18 @@
         <v>14</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>21</v>
@@ -5959,10 +6317,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H37" s="3">
         <v>41097.0</v>
@@ -5970,10 +6328,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>13</v>
@@ -5990,10 +6348,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>17</v>
@@ -6010,10 +6368,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>18</v>
@@ -6030,10 +6388,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H41" s="3">
         <v>40748.0</v>
@@ -6041,10 +6399,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>13</v>
@@ -6053,18 +6411,18 @@
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>17</v>
@@ -6073,18 +6431,18 @@
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>18</v>
@@ -6093,18 +6451,18 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>21</v>
@@ -6113,7 +6471,7 @@
         <v>22</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>16</v>
@@ -6121,10 +6479,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H46" s="3">
         <v>41168.5</v>
@@ -6132,7 +6490,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>12</v>
@@ -6144,15 +6502,15 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>12</v>
@@ -6164,15 +6522,15 @@
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>12</v>
@@ -6183,7 +6541,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>20</v>
@@ -6203,7 +6561,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>20</v>
@@ -6212,12 +6570,12 @@
         <v>17</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>20</v>
@@ -6228,7 +6586,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>26</v>
@@ -6237,12 +6595,12 @@
         <v>17</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>26</v>
@@ -6253,7 +6611,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>28</v>
@@ -6265,15 +6623,15 @@
         <v>14</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>28</v>
@@ -6285,15 +6643,15 @@
         <v>14</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>28</v>
@@ -6305,15 +6663,15 @@
         <v>14</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>28</v>
@@ -6324,10 +6682,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>13</v>
@@ -6344,10 +6702,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>17</v>
@@ -6364,10 +6722,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>18</v>
@@ -6384,30 +6742,30 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H63" s="3">
         <v>42226.0</v>
@@ -6415,10 +6773,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>13</v>
@@ -6435,10 +6793,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>17</v>
@@ -6455,10 +6813,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>18</v>
@@ -6475,10 +6833,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H67" s="3">
         <v>41364.0</v>
@@ -6486,10 +6844,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>13</v>
@@ -6498,18 +6856,18 @@
         <v>14</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>17</v>
@@ -6518,18 +6876,18 @@
         <v>14</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>18</v>
@@ -6538,18 +6896,18 @@
         <v>14</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>21</v>
@@ -6558,7 +6916,7 @@
         <v>22</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>16</v>
@@ -6566,10 +6924,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H72" s="3">
         <v>42114.0</v>
@@ -6577,7 +6935,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>12</v>
@@ -6597,7 +6955,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>12</v>
@@ -6617,7 +6975,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
@@ -6637,7 +6995,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
@@ -6648,7 +7006,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>20</v>
@@ -6668,7 +7026,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>20</v>
@@ -6677,12 +7035,12 @@
         <v>17</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>20</v>
@@ -6693,7 +7051,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>26</v>
@@ -6702,12 +7060,12 @@
         <v>17</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>26</v>
@@ -6718,7 +7076,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>28</v>
@@ -6738,7 +7096,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>28</v>
@@ -6758,7 +7116,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>28</v>
@@ -6778,7 +7136,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>28</v>
@@ -6789,10 +7147,10 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>13</v>
@@ -6809,10 +7167,10 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>17</v>
@@ -6829,10 +7187,10 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>18</v>
@@ -6849,10 +7207,10 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>21</v>
@@ -6869,10 +7227,10 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H90" s="3">
         <v>43312.0</v>
@@ -6880,10 +7238,10 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>13</v>
@@ -6900,10 +7258,10 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>17</v>
@@ -6920,10 +7278,10 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>18</v>
@@ -6940,10 +7298,10 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H94" s="3">
         <v>41988.0</v>
@@ -6951,10 +7309,10 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>13</v>
@@ -6963,32 +7321,32 @@
         <v>14</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>18</v>
@@ -6997,18 +7355,18 @@
         <v>14</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>21</v>
@@ -7017,7 +7375,7 @@
         <v>22</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>16</v>
@@ -7025,10 +7383,10 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H99" s="3">
         <v>41929.0</v>
@@ -7036,7 +7394,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>12</v>
@@ -7056,7 +7414,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>12</v>
@@ -7076,7 +7434,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>12</v>
@@ -7096,7 +7454,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>12</v>
@@ -7107,7 +7465,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>20</v>
@@ -7116,12 +7474,12 @@
         <v>17</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>20</v>
@@ -7141,7 +7499,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>20</v>
@@ -7199,24 +7557,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H3" s="3">
         <v>40004.0</v>
@@ -7224,7 +7582,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -7236,15 +7594,15 @@
         <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
@@ -7256,35 +7614,35 @@
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -7295,7 +7653,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>20</v>
@@ -7315,7 +7673,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
@@ -7324,12 +7682,12 @@
         <v>18</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>20</v>
@@ -7340,7 +7698,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>26</v>
@@ -7349,12 +7707,12 @@
         <v>18</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>26</v>
@@ -7365,7 +7723,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -7385,7 +7743,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
@@ -7405,7 +7763,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -7425,7 +7783,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -7436,10 +7794,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>13</v>
@@ -7456,10 +7814,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
@@ -7476,10 +7834,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>17</v>
@@ -7496,10 +7854,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>21</v>
@@ -7516,10 +7874,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H21" s="3">
         <v>40584.0</v>
@@ -7527,10 +7885,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>13</v>
@@ -7539,18 +7897,18 @@
         <v>14</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>18</v>
@@ -7559,18 +7917,18 @@
         <v>14</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>17</v>
@@ -7579,18 +7937,18 @@
         <v>14</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H25" s="3">
         <v>40437.5</v>
@@ -7598,10 +7956,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>13</v>
@@ -7618,10 +7976,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>18</v>
@@ -7638,10 +7996,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>17</v>
@@ -7658,10 +8016,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>21</v>
@@ -7670,18 +8028,18 @@
         <v>22</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H30" s="3">
         <v>40004.0</v>
@@ -7689,7 +8047,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
@@ -7709,7 +8067,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -7729,7 +8087,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -7749,7 +8107,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
@@ -7760,7 +8118,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>20</v>
@@ -7780,7 +8138,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>20</v>
@@ -7789,12 +8147,12 @@
         <v>17</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>20</v>
@@ -7805,7 +8163,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>26</v>
@@ -7814,12 +8172,12 @@
         <v>17</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>26</v>
@@ -7830,7 +8188,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -7850,7 +8208,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>28</v>
@@ -7870,7 +8228,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>28</v>
@@ -7881,10 +8239,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>18</v>
@@ -7893,18 +8251,18 @@
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>17</v>
@@ -7913,18 +8271,18 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>21</v>
@@ -7941,10 +8299,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H46" s="3">
         <v>41460.0</v>
@@ -7952,10 +8310,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>18</v>
@@ -7964,18 +8322,18 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>17</v>
@@ -7984,18 +8342,18 @@
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H49" s="3">
         <v>40886.0</v>
@@ -8003,10 +8361,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>13</v>
@@ -8015,18 +8373,18 @@
         <v>14</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>17</v>
@@ -8035,18 +8393,18 @@
         <v>14</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>18</v>
@@ -8058,15 +8416,15 @@
         <v>22</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>21</v>
@@ -8075,18 +8433,18 @@
         <v>22</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H54" s="3">
         <v>41250.0</v>
@@ -8094,7 +8452,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -8114,7 +8472,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
@@ -8134,7 +8492,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>12</v>
@@ -8154,7 +8512,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>12</v>
@@ -8165,7 +8523,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>20</v>
@@ -8185,7 +8543,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>20</v>
@@ -8194,12 +8552,12 @@
         <v>17</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>20</v>
@@ -8210,7 +8568,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>26</v>
@@ -8219,12 +8577,12 @@
         <v>17</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>26</v>
@@ -8235,7 +8593,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -8255,7 +8613,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>28</v>
@@ -8275,7 +8633,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>28</v>
@@ -8286,10 +8644,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>13</v>
@@ -8306,10 +8664,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>17</v>
@@ -8326,10 +8684,10 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>18</v>
@@ -8346,10 +8704,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>21</v>
@@ -8366,10 +8724,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H71" s="3">
         <v>42604.0</v>
@@ -8377,10 +8735,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>13</v>
@@ -8389,18 +8747,18 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>17</v>
@@ -8409,18 +8767,18 @@
         <v>14</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>18</v>
@@ -8432,15 +8790,15 @@
         <v>16</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H75" s="3">
         <v>41143.5</v>
@@ -8448,10 +8806,10 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>13</v>
@@ -8468,10 +8826,10 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>17</v>
@@ -8488,10 +8846,10 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>21</v>
@@ -8500,7 +8858,7 @@
         <v>22</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>16</v>
@@ -8508,10 +8866,10 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H79" s="3">
         <v>41784.0</v>
@@ -8519,7 +8877,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>12</v>
@@ -8531,15 +8889,15 @@
         <v>14</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>12</v>
@@ -8551,15 +8909,15 @@
         <v>14</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -8570,7 +8928,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>20</v>
@@ -8590,7 +8948,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>20</v>
@@ -8601,7 +8959,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>26</v>
@@ -8612,7 +8970,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>28</v>
@@ -8624,15 +8982,15 @@
         <v>14</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>28</v>
@@ -8644,15 +9002,15 @@
         <v>14</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -8664,15 +9022,15 @@
         <v>14</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -8683,10 +9041,10 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>13</v>
@@ -8703,10 +9061,10 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>17</v>
@@ -8723,10 +9081,10 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>18</v>
@@ -8743,10 +9101,10 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>21</v>
@@ -8763,10 +9121,10 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H94" s="3">
         <v>43464.0</v>
@@ -8774,10 +9132,10 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>13</v>
@@ -8794,10 +9152,10 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>17</v>
@@ -8814,10 +9172,10 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>18</v>
@@ -8834,10 +9192,10 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H98" s="3">
         <v>42008.0</v>
@@ -8845,10 +9203,10 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>13</v>
@@ -8865,10 +9223,10 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>17</v>
@@ -8885,10 +9243,10 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>18</v>
@@ -8905,10 +9263,10 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>21</v>
@@ -8917,7 +9275,7 @@
         <v>22</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>16</v>
@@ -8925,10 +9283,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H103" s="3">
         <v>43288.0</v>
@@ -8936,7 +9294,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>12</v>
@@ -8956,7 +9314,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>12</v>
@@ -8976,7 +9334,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>12</v>
@@ -8996,7 +9354,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>12</v>
@@ -9007,7 +9365,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>20</v>
@@ -9016,12 +9374,12 @@
         <v>17</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>20</v>
@@ -9041,7 +9399,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>20</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="193">
   <si>
     <t>Datum</t>
   </si>
@@ -138,12 +138,54 @@
     <t>09.05.2026</t>
   </si>
   <si>
+    <t>Lažek Jaroslav</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>Zadej tržbu</t>
+  </si>
+  <si>
     <t>10.05.2026</t>
   </si>
   <si>
     <t>11.05.2026</t>
   </si>
   <si>
+    <t>12.05.2026</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>13.05.2026</t>
+  </si>
+  <si>
+    <t>14.05.2026</t>
+  </si>
+  <si>
+    <t>15.05.2026</t>
+  </si>
+  <si>
+    <t>16.05.2026</t>
+  </si>
+  <si>
+    <t>17.05.2026</t>
+  </si>
+  <si>
+    <t>18.05.2026</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>19.05.2026</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
@@ -168,9 +210,6 @@
     <t>Chlubna Tomáš</t>
   </si>
   <si>
-    <t>14:30</t>
-  </si>
-  <si>
     <t>04:30</t>
   </si>
   <si>
@@ -186,12 +225,6 @@
     <t>10.04.2026</t>
   </si>
   <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
     <t>11.04.2026</t>
   </si>
   <si>
@@ -246,9 +279,6 @@
     <t>24.04.2026</t>
   </si>
   <si>
-    <t>08:30</t>
-  </si>
-  <si>
     <t>25.04.2026</t>
   </si>
   <si>
@@ -295,9 +325,6 @@
   </si>
   <si>
     <t>06:30</t>
-  </si>
-  <si>
-    <t>Zadej tržbu</t>
   </si>
   <si>
     <t>06.03.2026</t>
@@ -1352,50 +1379,121 @@
       <c r="B28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H28" s="3">
-        <v>40004.0</v>
-      </c>
+      <c r="C28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="3">
-        <v>40004.0</v>
+        <v>20</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="P29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM29" s="1" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AN29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AQ29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS29" s="1" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AT29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU29" s="1" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AV29" s="1" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="H30" s="3">
+        <v>40004.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>14</v>
@@ -1409,13 +1507,441 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="3">
+      <c r="C32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" s="3">
         <v>40660.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37" s="3">
+        <v>41230.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" s="3">
+        <v>40900.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" s="3">
+        <v>41356.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="3">
+        <v>40900.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" s="3">
+        <v>40004.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H49" s="3">
+        <v>40004.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H52" s="3">
+        <v>40752.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H57" s="3">
+        <v>42064.0</v>
       </c>
     </row>
   </sheetData>
@@ -1467,7 +1993,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>32</v>
@@ -1487,7 +2013,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>32</v>
@@ -1507,7 +2033,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>32</v>
@@ -1527,7 +2053,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>32</v>
@@ -1538,7 +2064,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>34</v>
@@ -1558,7 +2084,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>34</v>
@@ -1578,7 +2104,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>34</v>
@@ -1598,7 +2124,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>34</v>
@@ -1618,7 +2144,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>34</v>
@@ -1629,7 +2155,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -1649,7 +2175,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
@@ -1669,7 +2195,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -1689,7 +2215,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -1700,7 +2226,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>20</v>
@@ -1720,7 +2246,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>20</v>
@@ -1731,7 +2257,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>26</v>
@@ -1742,7 +2268,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>28</v>
@@ -1762,7 +2288,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>28</v>
@@ -1782,7 +2308,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>28</v>
@@ -1802,7 +2328,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>28</v>
@@ -1813,7 +2339,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -1833,7 +2359,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>30</v>
@@ -1853,7 +2379,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>30</v>
@@ -1873,27 +2399,27 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>30</v>
@@ -1902,18 +2428,18 @@
         <v>21</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>30</v>
@@ -1924,7 +2450,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>32</v>
@@ -1944,7 +2470,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>32</v>
@@ -1964,7 +2490,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>32</v>
@@ -1984,7 +2510,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>32</v>
@@ -1995,7 +2521,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>34</v>
@@ -2015,7 +2541,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>34</v>
@@ -2035,7 +2561,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>34</v>
@@ -2055,7 +2581,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>34</v>
@@ -2075,7 +2601,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>34</v>
@@ -2086,7 +2612,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>12</v>
@@ -2098,15 +2624,15 @@
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>12</v>
@@ -2118,15 +2644,15 @@
         <v>14</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>12</v>
@@ -2138,15 +2664,15 @@
         <v>14</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>12</v>
@@ -2157,7 +2683,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>20</v>
@@ -2177,7 +2703,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>20</v>
@@ -2188,7 +2714,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>26</v>
@@ -2199,7 +2725,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>28</v>
@@ -2219,7 +2745,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>28</v>
@@ -2239,7 +2765,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>28</v>
@@ -2250,7 +2776,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>30</v>
@@ -2270,7 +2796,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>30</v>
@@ -2290,19 +2816,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -2310,7 +2836,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -2319,10 +2845,10 @@
         <v>21</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>14</v>
@@ -2330,7 +2856,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
@@ -2341,7 +2867,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>32</v>
@@ -2361,7 +2887,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>32</v>
@@ -2381,7 +2907,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>32</v>
@@ -2401,7 +2927,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>32</v>
@@ -2412,7 +2938,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>34</v>
@@ -2432,7 +2958,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>34</v>
@@ -2452,7 +2978,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>34</v>
@@ -2472,7 +2998,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>34</v>
@@ -2492,7 +3018,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>34</v>
@@ -2503,7 +3029,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>12</v>
@@ -2523,7 +3049,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>12</v>
@@ -2543,7 +3069,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>12</v>
@@ -2554,7 +3080,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>20</v>
@@ -2574,7 +3100,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>20</v>
@@ -2585,7 +3111,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>26</v>
@@ -2596,7 +3122,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>28</v>
@@ -2616,7 +3142,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>28</v>
@@ -2636,7 +3162,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>28</v>
@@ -2647,7 +3173,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>30</v>
@@ -2667,7 +3193,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>30</v>
@@ -2687,19 +3213,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>14</v>
@@ -2707,7 +3233,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>30</v>
@@ -2716,18 +3242,18 @@
         <v>21</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>30</v>
@@ -2738,7 +3264,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>32</v>
@@ -2758,7 +3284,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>32</v>
@@ -2778,7 +3304,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>32</v>
@@ -2789,7 +3315,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>34</v>
@@ -2809,7 +3335,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>34</v>
@@ -2829,7 +3355,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>34</v>
@@ -2849,7 +3375,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>34</v>
@@ -2860,7 +3386,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -2872,15 +3398,15 @@
         <v>14</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
@@ -2892,15 +3418,15 @@
         <v>14</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>12</v>
@@ -2911,7 +3437,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>20</v>
@@ -2931,7 +3457,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>20</v>
@@ -2942,7 +3468,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>26</v>
@@ -2953,7 +3479,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -2973,7 +3499,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -2993,7 +3519,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>28</v>
@@ -3004,7 +3530,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>30</v>
@@ -3024,7 +3550,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>30</v>
@@ -3044,27 +3570,27 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>30</v>
@@ -3073,18 +3599,18 @@
         <v>21</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>30</v>
@@ -3095,7 +3621,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>32</v>
@@ -3115,7 +3641,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>32</v>
@@ -3135,7 +3661,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>32</v>
@@ -3146,7 +3672,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>34</v>
@@ -3166,7 +3692,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>34</v>
@@ -3186,7 +3712,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>34</v>
@@ -3206,7 +3732,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>34</v>
@@ -3226,7 +3752,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>34</v>
@@ -3284,7 +3810,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -3293,12 +3819,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>26</v>
@@ -3309,7 +3835,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -3329,7 +3855,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -3349,7 +3875,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>28</v>
@@ -3369,7 +3895,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -3380,7 +3906,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -3400,7 +3926,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
@@ -3420,7 +3946,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -3435,12 +3961,12 @@
         <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>30</v>
@@ -3460,7 +3986,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>30</v>
@@ -3471,7 +3997,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>32</v>
@@ -3491,7 +4017,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>32</v>
@@ -3511,7 +4037,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
@@ -3531,7 +4057,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>32</v>
@@ -3542,7 +4068,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>34</v>
@@ -3562,7 +4088,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>34</v>
@@ -3574,15 +4100,15 @@
         <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>34</v>
@@ -3594,15 +4120,15 @@
         <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>34</v>
@@ -3622,7 +4148,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>34</v>
@@ -3635,12 +4161,12 @@
         <v>40483.5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>34</v>
@@ -3677,7 +4203,7 @@
         <v>0.0</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="AI22" s="3">
         <v>0.0</v>
@@ -3724,7 +4250,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>12</v>
@@ -3744,7 +4270,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>12</v>
@@ -3764,7 +4290,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>12</v>
@@ -3784,7 +4310,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>12</v>
@@ -3795,7 +4321,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>20</v>
@@ -3815,7 +4341,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>20</v>
@@ -3824,12 +4350,12 @@
         <v>17</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>20</v>
@@ -3840,7 +4366,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>26</v>
@@ -3849,12 +4375,12 @@
         <v>17</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>26</v>
@@ -3865,7 +4391,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
@@ -3885,7 +4411,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>28</v>
@@ -3905,7 +4431,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>28</v>
@@ -3925,7 +4451,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>28</v>
@@ -3936,7 +4462,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
@@ -3956,7 +4482,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>30</v>
@@ -3968,15 +4494,15 @@
         <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>30</v>
@@ -3996,7 +4522,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>30</v>
@@ -4016,7 +4542,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>30</v>
@@ -4029,12 +4555,12 @@
         <v>41160.0</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>30</v>
@@ -4071,7 +4597,7 @@
         <v>0.0</v>
       </c>
       <c r="AD41" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="AI41" s="3">
         <v>0.0</v>
@@ -4118,7 +4644,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>32</v>
@@ -4138,7 +4664,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>32</v>
@@ -4158,7 +4684,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>32</v>
@@ -4178,7 +4704,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>32</v>
@@ -4189,7 +4715,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>34</v>
@@ -4209,7 +4735,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>34</v>
@@ -4221,15 +4747,15 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>34</v>
@@ -4241,15 +4767,15 @@
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>34</v>
@@ -4269,7 +4795,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>34</v>
@@ -4282,12 +4808,12 @@
         <v>41286.0</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>34</v>
@@ -4324,7 +4850,7 @@
         <v>0.0</v>
       </c>
       <c r="AD51" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="AI51" s="3">
         <v>0.0</v>
@@ -4371,7 +4897,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>12</v>
@@ -4391,7 +4917,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>12</v>
@@ -4411,7 +4937,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>12</v>
@@ -4431,7 +4957,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -4442,7 +4968,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>20</v>
@@ -4462,7 +4988,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>20</v>
@@ -4471,12 +4997,12 @@
         <v>17</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>20</v>
@@ -4487,7 +5013,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>26</v>
@@ -4496,12 +5022,12 @@
         <v>17</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>26</v>
@@ -4512,7 +5038,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>28</v>
@@ -4532,7 +5058,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>28</v>
@@ -4552,7 +5078,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>28</v>
@@ -4572,7 +5098,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -4583,7 +5109,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>30</v>
@@ -4603,7 +5129,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>30</v>
@@ -4623,7 +5149,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>30</v>
@@ -4643,7 +5169,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>30</v>
@@ -4663,7 +5189,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>30</v>
@@ -4674,7 +5200,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>32</v>
@@ -4694,7 +5220,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>32</v>
@@ -4706,15 +5232,15 @@
         <v>14</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>32</v>
@@ -4726,15 +5252,15 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>32</v>
@@ -4747,12 +5273,12 @@
         <v>41264.0</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>32</v>
@@ -4789,7 +5315,7 @@
         <v>0.0</v>
       </c>
       <c r="AD74" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="AI74" s="3">
         <v>0.0</v>
@@ -4836,7 +5362,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>34</v>
@@ -4856,7 +5382,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>34</v>
@@ -4876,7 +5402,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>34</v>
@@ -4896,7 +5422,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>34</v>
@@ -4907,7 +5433,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>12</v>
@@ -4927,7 +5453,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>12</v>
@@ -4947,7 +5473,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>12</v>
@@ -4967,7 +5493,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -4978,7 +5504,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>20</v>
@@ -4998,7 +5524,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>20</v>
@@ -5007,12 +5533,12 @@
         <v>17</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>20</v>
@@ -5023,7 +5549,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>26</v>
@@ -5032,12 +5558,12 @@
         <v>17</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>26</v>
@@ -5048,7 +5574,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -5068,7 +5594,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -5088,7 +5614,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>28</v>
@@ -5099,7 +5625,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>30</v>
@@ -5119,7 +5645,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>30</v>
@@ -5128,12 +5654,12 @@
         <v>17</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>30</v>
@@ -5153,7 +5679,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>30</v>
@@ -5173,7 +5699,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>30</v>
@@ -5184,7 +5710,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>32</v>
@@ -5204,7 +5730,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>32</v>
@@ -5224,7 +5750,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>32</v>
@@ -5244,7 +5770,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>32</v>
@@ -5255,7 +5781,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>34</v>
@@ -5275,7 +5801,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>34</v>
@@ -5295,7 +5821,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>34</v>
@@ -5315,7 +5841,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>34</v>
@@ -5335,7 +5861,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>34</v>
@@ -5346,7 +5872,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>12</v>
@@ -5366,7 +5892,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>12</v>
@@ -5386,7 +5912,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>12</v>
@@ -5406,7 +5932,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>12</v>
@@ -5417,7 +5943,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>20</v>
@@ -5437,7 +5963,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>20</v>
@@ -5446,12 +5972,12 @@
         <v>17</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>20</v>
@@ -5462,7 +5988,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>26</v>
@@ -5471,12 +5997,12 @@
         <v>17</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>26</v>
@@ -5487,7 +6013,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>28</v>
@@ -5507,7 +6033,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>28</v>
@@ -5527,7 +6053,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>28</v>
@@ -5547,7 +6073,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>28</v>
@@ -5558,7 +6084,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>30</v>
@@ -5578,7 +6104,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>30</v>
@@ -5598,7 +6124,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>30</v>
@@ -5618,19 +6144,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>14</v>
@@ -5638,7 +6164,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>30</v>
@@ -5647,7 +6173,7 @@
         <v>21</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>23</v>
@@ -5658,7 +6184,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>30</v>
@@ -5716,7 +6242,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -5725,12 +6251,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>26</v>
@@ -5741,7 +6267,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -5761,7 +6287,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -5781,7 +6307,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>28</v>
@@ -5801,7 +6327,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -5812,7 +6338,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -5824,15 +6350,15 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
@@ -5844,15 +6370,15 @@
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -5864,15 +6390,15 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>30</v>
@@ -5892,7 +6418,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>30</v>
@@ -5903,7 +6429,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>32</v>
@@ -5923,7 +6449,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>32</v>
@@ -5943,7 +6469,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
@@ -5954,7 +6480,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>34</v>
@@ -5974,7 +6500,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>34</v>
@@ -5994,7 +6520,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>34</v>
@@ -6014,7 +6540,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>34</v>
@@ -6025,7 +6551,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -6045,7 +6571,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>12</v>
@@ -6065,7 +6591,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>12</v>
@@ -6085,7 +6611,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>12</v>
@@ -6096,7 +6622,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>20</v>
@@ -6116,7 +6642,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>20</v>
@@ -6125,12 +6651,12 @@
         <v>17</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>20</v>
@@ -6141,7 +6667,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>26</v>
@@ -6150,12 +6676,12 @@
         <v>17</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>26</v>
@@ -6166,7 +6692,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
@@ -6186,7 +6712,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -6206,7 +6732,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -6226,7 +6752,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
@@ -6237,7 +6763,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>30</v>
@@ -6249,15 +6775,15 @@
         <v>14</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
@@ -6269,15 +6795,15 @@
         <v>14</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>30</v>
@@ -6289,15 +6815,15 @@
         <v>14</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
@@ -6317,7 +6843,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>30</v>
@@ -6328,7 +6854,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>32</v>
@@ -6348,7 +6874,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>32</v>
@@ -6368,7 +6894,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>32</v>
@@ -6388,7 +6914,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>32</v>
@@ -6399,7 +6925,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>34</v>
@@ -6411,15 +6937,15 @@
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>34</v>
@@ -6431,15 +6957,15 @@
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>34</v>
@@ -6451,15 +6977,15 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>34</v>
@@ -6479,7 +7005,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>34</v>
@@ -6490,7 +7016,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>12</v>
@@ -6502,15 +7028,15 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>12</v>
@@ -6522,15 +7048,15 @@
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>12</v>
@@ -6541,7 +7067,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>20</v>
@@ -6561,7 +7087,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>20</v>
@@ -6570,12 +7096,12 @@
         <v>17</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>20</v>
@@ -6586,7 +7112,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>26</v>
@@ -6595,12 +7121,12 @@
         <v>17</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>26</v>
@@ -6611,7 +7137,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>28</v>
@@ -6631,7 +7157,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>28</v>
@@ -6651,7 +7177,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>28</v>
@@ -6671,7 +7197,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>28</v>
@@ -6682,7 +7208,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>30</v>
@@ -6702,7 +7228,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>30</v>
@@ -6722,7 +7248,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>30</v>
@@ -6742,7 +7268,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>30</v>
@@ -6751,18 +7277,18 @@
         <v>21</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>30</v>
@@ -6773,7 +7299,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>32</v>
@@ -6793,7 +7319,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>32</v>
@@ -6813,7 +7339,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>32</v>
@@ -6833,7 +7359,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>32</v>
@@ -6844,7 +7370,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>34</v>
@@ -6856,15 +7382,15 @@
         <v>14</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>34</v>
@@ -6876,15 +7402,15 @@
         <v>14</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>34</v>
@@ -6896,15 +7422,15 @@
         <v>14</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>34</v>
@@ -6924,7 +7450,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>34</v>
@@ -6935,7 +7461,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>12</v>
@@ -6955,7 +7481,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>12</v>
@@ -6975,7 +7501,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
@@ -6995,7 +7521,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
@@ -7006,7 +7532,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>20</v>
@@ -7026,7 +7552,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>20</v>
@@ -7035,12 +7561,12 @@
         <v>17</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>20</v>
@@ -7051,7 +7577,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>26</v>
@@ -7060,12 +7586,12 @@
         <v>17</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>26</v>
@@ -7076,7 +7602,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>28</v>
@@ -7096,7 +7622,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>28</v>
@@ -7116,7 +7642,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>28</v>
@@ -7136,7 +7662,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>28</v>
@@ -7147,7 +7673,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>30</v>
@@ -7167,7 +7693,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>30</v>
@@ -7187,7 +7713,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>30</v>
@@ -7207,7 +7733,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>30</v>
@@ -7227,7 +7753,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>30</v>
@@ -7238,7 +7764,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>32</v>
@@ -7258,7 +7784,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>32</v>
@@ -7278,7 +7804,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>32</v>
@@ -7298,7 +7824,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>32</v>
@@ -7309,7 +7835,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>34</v>
@@ -7321,15 +7847,15 @@
         <v>14</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>34</v>
@@ -7338,12 +7864,12 @@
         <v>17</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>34</v>
@@ -7355,15 +7881,15 @@
         <v>14</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>34</v>
@@ -7383,7 +7909,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>34</v>
@@ -7394,7 +7920,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>12</v>
@@ -7414,7 +7940,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>12</v>
@@ -7434,7 +7960,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>12</v>
@@ -7454,7 +7980,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>12</v>
@@ -7465,7 +7991,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>20</v>
@@ -7474,12 +8000,12 @@
         <v>17</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>20</v>
@@ -7499,7 +8025,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>20</v>
@@ -7557,7 +8083,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>34</v>
@@ -7566,12 +8092,12 @@
         <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>34</v>
@@ -7582,7 +8108,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -7594,15 +8120,15 @@
         <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
@@ -7614,35 +8140,35 @@
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -7653,7 +8179,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>20</v>
@@ -7673,7 +8199,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
@@ -7682,12 +8208,12 @@
         <v>18</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>20</v>
@@ -7698,7 +8224,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>26</v>
@@ -7707,12 +8233,12 @@
         <v>18</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>26</v>
@@ -7723,7 +8249,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -7743,7 +8269,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
@@ -7763,7 +8289,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -7783,7 +8309,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -7794,7 +8320,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
@@ -7814,7 +8340,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
@@ -7834,7 +8360,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -7854,7 +8380,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -7874,7 +8400,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
@@ -7885,7 +8411,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>32</v>
@@ -7897,15 +8423,15 @@
         <v>14</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>32</v>
@@ -7917,15 +8443,15 @@
         <v>14</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>32</v>
@@ -7937,15 +8463,15 @@
         <v>14</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>32</v>
@@ -7956,7 +8482,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>34</v>
@@ -7976,7 +8502,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>34</v>
@@ -7996,7 +8522,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>34</v>
@@ -8016,7 +8542,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>34</v>
@@ -8028,15 +8554,15 @@
         <v>22</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>34</v>
@@ -8047,7 +8573,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
@@ -8067,7 +8593,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -8087,7 +8613,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -8107,7 +8633,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
@@ -8118,7 +8644,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>20</v>
@@ -8138,7 +8664,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>20</v>
@@ -8147,12 +8673,12 @@
         <v>17</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>20</v>
@@ -8163,7 +8689,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>26</v>
@@ -8172,12 +8698,12 @@
         <v>17</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>26</v>
@@ -8188,7 +8714,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -8208,7 +8734,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>28</v>
@@ -8228,7 +8754,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>28</v>
@@ -8239,7 +8765,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
@@ -8251,15 +8777,15 @@
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -8271,15 +8797,15 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>30</v>
@@ -8299,7 +8825,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -8310,7 +8836,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>32</v>
@@ -8322,15 +8848,15 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>32</v>
@@ -8342,15 +8868,15 @@
         <v>14</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>32</v>
@@ -8361,7 +8887,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>34</v>
@@ -8373,15 +8899,15 @@
         <v>14</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>34</v>
@@ -8393,15 +8919,15 @@
         <v>14</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>34</v>
@@ -8416,12 +8942,12 @@
         <v>22</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>34</v>
@@ -8433,15 +8959,15 @@
         <v>22</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>34</v>
@@ -8452,7 +8978,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -8472,7 +8998,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
@@ -8492,7 +9018,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>12</v>
@@ -8512,7 +9038,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>12</v>
@@ -8523,7 +9049,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>20</v>
@@ -8543,7 +9069,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>20</v>
@@ -8552,12 +9078,12 @@
         <v>17</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>20</v>
@@ -8568,7 +9094,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>26</v>
@@ -8577,12 +9103,12 @@
         <v>17</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>26</v>
@@ -8593,7 +9119,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -8613,7 +9139,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>28</v>
@@ -8633,7 +9159,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>28</v>
@@ -8644,7 +9170,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>30</v>
@@ -8664,7 +9190,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>30</v>
@@ -8684,7 +9210,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>30</v>
@@ -8704,7 +9230,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>30</v>
@@ -8724,7 +9250,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>30</v>
@@ -8735,7 +9261,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>32</v>
@@ -8747,15 +9273,15 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>32</v>
@@ -8767,15 +9293,15 @@
         <v>14</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>32</v>
@@ -8790,12 +9316,12 @@
         <v>16</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>32</v>
@@ -8806,7 +9332,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>34</v>
@@ -8826,7 +9352,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>34</v>
@@ -8846,7 +9372,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>34</v>
@@ -8866,7 +9392,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>34</v>
@@ -8877,7 +9403,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>12</v>
@@ -8889,15 +9415,15 @@
         <v>14</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>12</v>
@@ -8909,15 +9435,15 @@
         <v>14</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -8928,7 +9454,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>20</v>
@@ -8948,7 +9474,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>20</v>
@@ -8959,7 +9485,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>26</v>
@@ -8970,7 +9496,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>28</v>
@@ -8982,15 +9508,15 @@
         <v>14</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>28</v>
@@ -9002,15 +9528,15 @@
         <v>14</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -9022,15 +9548,15 @@
         <v>14</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -9041,7 +9567,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>30</v>
@@ -9061,7 +9587,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>30</v>
@@ -9081,7 +9607,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>30</v>
@@ -9101,7 +9627,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>30</v>
@@ -9121,7 +9647,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>30</v>
@@ -9132,7 +9658,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>32</v>
@@ -9152,7 +9678,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>32</v>
@@ -9172,7 +9698,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>32</v>
@@ -9192,7 +9718,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>32</v>
@@ -9203,7 +9729,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>34</v>
@@ -9223,7 +9749,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>34</v>
@@ -9243,7 +9769,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>34</v>
@@ -9263,7 +9789,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>34</v>
@@ -9283,7 +9809,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>34</v>
@@ -9294,7 +9820,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>12</v>
@@ -9314,7 +9840,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>12</v>
@@ -9334,7 +9860,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>12</v>
@@ -9354,7 +9880,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>12</v>
@@ -9365,7 +9891,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>20</v>
@@ -9374,12 +9900,12 @@
         <v>17</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>20</v>
@@ -9399,7 +9925,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>20</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="195">
   <si>
     <t>Datum</t>
   </si>
@@ -184,6 +184,12 @@
   </si>
   <si>
     <t>19.05.2026</t>
+  </si>
+  <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>21.05.2026</t>
   </si>
   <si>
     <t>01.04.2026</t>
@@ -1944,6 +1950,168 @@
         <v>42064.0</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H61" s="3">
+        <v>41284.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H66" s="3">
+        <v>41823.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1993,7 +2161,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>32</v>
@@ -2013,7 +2181,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>32</v>
@@ -2033,7 +2201,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>32</v>
@@ -2053,7 +2221,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>32</v>
@@ -2064,7 +2232,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>34</v>
@@ -2084,7 +2252,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>34</v>
@@ -2104,7 +2272,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>34</v>
@@ -2124,7 +2292,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>34</v>
@@ -2144,7 +2312,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>34</v>
@@ -2155,7 +2323,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -2175,7 +2343,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
@@ -2195,7 +2363,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -2215,7 +2383,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -2226,7 +2394,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>20</v>
@@ -2246,7 +2414,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>20</v>
@@ -2257,7 +2425,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>26</v>
@@ -2268,7 +2436,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>28</v>
@@ -2288,7 +2456,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>28</v>
@@ -2308,7 +2476,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>28</v>
@@ -2328,7 +2496,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>28</v>
@@ -2339,7 +2507,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -2359,7 +2527,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>30</v>
@@ -2379,7 +2547,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>30</v>
@@ -2399,13 +2567,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>22</v>
@@ -2414,12 +2582,12 @@
         <v>53</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>30</v>
@@ -2434,12 +2602,12 @@
         <v>23</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>30</v>
@@ -2450,7 +2618,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>32</v>
@@ -2470,7 +2638,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>32</v>
@@ -2490,7 +2658,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>32</v>
@@ -2510,7 +2678,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>32</v>
@@ -2521,7 +2689,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>34</v>
@@ -2541,7 +2709,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>34</v>
@@ -2561,7 +2729,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>34</v>
@@ -2581,7 +2749,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>34</v>
@@ -2601,7 +2769,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>34</v>
@@ -2612,7 +2780,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>12</v>
@@ -2632,7 +2800,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>12</v>
@@ -2652,7 +2820,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>12</v>
@@ -2672,7 +2840,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>12</v>
@@ -2683,7 +2851,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>20</v>
@@ -2703,7 +2871,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>20</v>
@@ -2714,7 +2882,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>26</v>
@@ -2725,7 +2893,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>28</v>
@@ -2745,7 +2913,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>28</v>
@@ -2765,7 +2933,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>28</v>
@@ -2776,7 +2944,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>30</v>
@@ -2796,7 +2964,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>30</v>
@@ -2816,19 +2984,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -2836,7 +3004,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -2845,10 +3013,10 @@
         <v>21</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>14</v>
@@ -2856,7 +3024,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
@@ -2867,7 +3035,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>32</v>
@@ -2887,7 +3055,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>32</v>
@@ -2907,7 +3075,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>32</v>
@@ -2927,7 +3095,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>32</v>
@@ -2938,7 +3106,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>34</v>
@@ -2958,7 +3126,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>34</v>
@@ -2978,7 +3146,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>34</v>
@@ -2998,7 +3166,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>34</v>
@@ -3018,7 +3186,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>34</v>
@@ -3029,7 +3197,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>12</v>
@@ -3049,7 +3217,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>12</v>
@@ -3069,7 +3237,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>12</v>
@@ -3080,7 +3248,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>20</v>
@@ -3100,7 +3268,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>20</v>
@@ -3111,7 +3279,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>26</v>
@@ -3122,7 +3290,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>28</v>
@@ -3142,7 +3310,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>28</v>
@@ -3162,7 +3330,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>28</v>
@@ -3173,7 +3341,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>30</v>
@@ -3193,7 +3361,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>30</v>
@@ -3213,19 +3381,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>14</v>
@@ -3233,7 +3401,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>30</v>
@@ -3242,18 +3410,18 @@
         <v>21</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>30</v>
@@ -3264,7 +3432,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>32</v>
@@ -3284,7 +3452,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>32</v>
@@ -3304,7 +3472,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>32</v>
@@ -3315,7 +3483,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>34</v>
@@ -3335,7 +3503,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>34</v>
@@ -3355,7 +3523,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>34</v>
@@ -3375,7 +3543,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>34</v>
@@ -3386,7 +3554,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -3406,7 +3574,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
@@ -3426,7 +3594,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>12</v>
@@ -3437,7 +3605,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>20</v>
@@ -3457,7 +3625,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>20</v>
@@ -3468,7 +3636,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>26</v>
@@ -3479,7 +3647,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -3499,7 +3667,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -3519,7 +3687,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>28</v>
@@ -3530,7 +3698,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>30</v>
@@ -3550,7 +3718,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>30</v>
@@ -3570,27 +3738,27 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>30</v>
@@ -3599,18 +3767,18 @@
         <v>21</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>30</v>
@@ -3621,7 +3789,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>32</v>
@@ -3641,7 +3809,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>32</v>
@@ -3661,7 +3829,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>32</v>
@@ -3672,7 +3840,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>34</v>
@@ -3692,7 +3860,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>34</v>
@@ -3712,7 +3880,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>34</v>
@@ -3732,7 +3900,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>34</v>
@@ -3752,7 +3920,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>34</v>
@@ -3810,7 +3978,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -3819,12 +3987,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>26</v>
@@ -3835,7 +4003,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -3855,7 +4023,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -3875,7 +4043,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>28</v>
@@ -3895,7 +4063,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -3906,7 +4074,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -3926,7 +4094,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
@@ -3946,7 +4114,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -3961,12 +4129,12 @@
         <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>30</v>
@@ -3986,7 +4154,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>30</v>
@@ -3997,7 +4165,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>32</v>
@@ -4017,7 +4185,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>32</v>
@@ -4037,7 +4205,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
@@ -4057,7 +4225,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>32</v>
@@ -4068,7 +4236,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>34</v>
@@ -4088,7 +4256,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>34</v>
@@ -4100,15 +4268,15 @@
         <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>34</v>
@@ -4120,15 +4288,15 @@
         <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>34</v>
@@ -4148,7 +4316,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>34</v>
@@ -4161,12 +4329,12 @@
         <v>40483.5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>34</v>
@@ -4250,7 +4418,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>12</v>
@@ -4270,7 +4438,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>12</v>
@@ -4290,7 +4458,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>12</v>
@@ -4310,7 +4478,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>12</v>
@@ -4321,7 +4489,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>20</v>
@@ -4341,7 +4509,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>20</v>
@@ -4350,12 +4518,12 @@
         <v>17</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>20</v>
@@ -4366,7 +4534,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>26</v>
@@ -4375,12 +4543,12 @@
         <v>17</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>26</v>
@@ -4391,7 +4559,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
@@ -4411,7 +4579,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>28</v>
@@ -4431,7 +4599,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>28</v>
@@ -4451,7 +4619,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>28</v>
@@ -4462,7 +4630,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
@@ -4482,7 +4650,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>30</v>
@@ -4502,7 +4670,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>30</v>
@@ -4522,7 +4690,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>30</v>
@@ -4542,7 +4710,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>30</v>
@@ -4555,12 +4723,12 @@
         <v>41160.0</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>30</v>
@@ -4644,7 +4812,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>32</v>
@@ -4664,7 +4832,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>32</v>
@@ -4684,7 +4852,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>32</v>
@@ -4704,7 +4872,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>32</v>
@@ -4715,7 +4883,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>34</v>
@@ -4735,7 +4903,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>34</v>
@@ -4755,7 +4923,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>34</v>
@@ -4775,7 +4943,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>34</v>
@@ -4795,7 +4963,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>34</v>
@@ -4808,12 +4976,12 @@
         <v>41286.0</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>34</v>
@@ -4897,7 +5065,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>12</v>
@@ -4917,7 +5085,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>12</v>
@@ -4937,7 +5105,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>12</v>
@@ -4957,7 +5125,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -4968,7 +5136,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>20</v>
@@ -4988,7 +5156,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>20</v>
@@ -4997,12 +5165,12 @@
         <v>17</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>20</v>
@@ -5013,7 +5181,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>26</v>
@@ -5022,12 +5190,12 @@
         <v>17</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>26</v>
@@ -5038,7 +5206,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>28</v>
@@ -5058,7 +5226,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>28</v>
@@ -5078,7 +5246,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>28</v>
@@ -5098,7 +5266,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -5109,7 +5277,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>30</v>
@@ -5129,7 +5297,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>30</v>
@@ -5149,7 +5317,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>30</v>
@@ -5169,7 +5337,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>30</v>
@@ -5189,7 +5357,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>30</v>
@@ -5200,7 +5368,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>32</v>
@@ -5220,7 +5388,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>32</v>
@@ -5240,7 +5408,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>32</v>
@@ -5260,7 +5428,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>32</v>
@@ -5273,12 +5441,12 @@
         <v>41264.0</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>32</v>
@@ -5362,7 +5530,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>34</v>
@@ -5382,7 +5550,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>34</v>
@@ -5402,7 +5570,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>34</v>
@@ -5422,7 +5590,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>34</v>
@@ -5433,7 +5601,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>12</v>
@@ -5453,7 +5621,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>12</v>
@@ -5473,7 +5641,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>12</v>
@@ -5493,7 +5661,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -5504,7 +5672,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>20</v>
@@ -5524,7 +5692,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>20</v>
@@ -5533,12 +5701,12 @@
         <v>17</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>20</v>
@@ -5549,7 +5717,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>26</v>
@@ -5558,12 +5726,12 @@
         <v>17</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>26</v>
@@ -5574,7 +5742,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -5594,7 +5762,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -5614,7 +5782,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>28</v>
@@ -5625,7 +5793,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>30</v>
@@ -5645,7 +5813,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>30</v>
@@ -5654,12 +5822,12 @@
         <v>17</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>30</v>
@@ -5679,7 +5847,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>30</v>
@@ -5699,7 +5867,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>30</v>
@@ -5710,7 +5878,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>32</v>
@@ -5730,7 +5898,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>32</v>
@@ -5750,7 +5918,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>32</v>
@@ -5770,7 +5938,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>32</v>
@@ -5781,7 +5949,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>34</v>
@@ -5801,7 +5969,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>34</v>
@@ -5821,7 +5989,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>34</v>
@@ -5841,7 +6009,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>34</v>
@@ -5861,7 +6029,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>34</v>
@@ -5872,7 +6040,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>12</v>
@@ -5892,7 +6060,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>12</v>
@@ -5912,7 +6080,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>12</v>
@@ -5932,7 +6100,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>12</v>
@@ -5943,7 +6111,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>20</v>
@@ -5963,7 +6131,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>20</v>
@@ -5972,12 +6140,12 @@
         <v>17</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>20</v>
@@ -5988,7 +6156,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>26</v>
@@ -5997,12 +6165,12 @@
         <v>17</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>26</v>
@@ -6013,7 +6181,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>28</v>
@@ -6033,7 +6201,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>28</v>
@@ -6053,7 +6221,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>28</v>
@@ -6073,7 +6241,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>28</v>
@@ -6084,7 +6252,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>30</v>
@@ -6104,7 +6272,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>30</v>
@@ -6124,7 +6292,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>30</v>
@@ -6144,19 +6312,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>14</v>
@@ -6164,7 +6332,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>30</v>
@@ -6173,7 +6341,7 @@
         <v>21</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>23</v>
@@ -6184,7 +6352,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>30</v>
@@ -6242,7 +6410,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -6251,12 +6419,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>26</v>
@@ -6267,7 +6435,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -6287,7 +6455,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -6307,7 +6475,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>28</v>
@@ -6327,7 +6495,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -6338,7 +6506,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -6350,15 +6518,15 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
@@ -6370,15 +6538,15 @@
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -6390,15 +6558,15 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>30</v>
@@ -6418,7 +6586,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>30</v>
@@ -6429,7 +6597,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>32</v>
@@ -6449,7 +6617,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>32</v>
@@ -6469,7 +6637,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
@@ -6480,7 +6648,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>34</v>
@@ -6500,7 +6668,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>34</v>
@@ -6520,7 +6688,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>34</v>
@@ -6540,7 +6708,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>34</v>
@@ -6551,7 +6719,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -6571,7 +6739,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>12</v>
@@ -6591,7 +6759,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>12</v>
@@ -6611,7 +6779,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>12</v>
@@ -6622,7 +6790,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>20</v>
@@ -6642,7 +6810,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>20</v>
@@ -6651,12 +6819,12 @@
         <v>17</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>20</v>
@@ -6667,7 +6835,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>26</v>
@@ -6676,12 +6844,12 @@
         <v>17</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>26</v>
@@ -6692,7 +6860,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
@@ -6712,7 +6880,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -6732,7 +6900,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -6752,7 +6920,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
@@ -6763,7 +6931,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>30</v>
@@ -6783,7 +6951,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
@@ -6803,7 +6971,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>30</v>
@@ -6823,7 +6991,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
@@ -6843,7 +7011,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>30</v>
@@ -6854,7 +7022,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>32</v>
@@ -6874,7 +7042,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>32</v>
@@ -6894,7 +7062,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>32</v>
@@ -6914,7 +7082,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>32</v>
@@ -6925,7 +7093,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>34</v>
@@ -6937,15 +7105,15 @@
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>34</v>
@@ -6957,15 +7125,15 @@
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>34</v>
@@ -6977,15 +7145,15 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>34</v>
@@ -7005,7 +7173,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>34</v>
@@ -7016,7 +7184,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>12</v>
@@ -7036,7 +7204,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>12</v>
@@ -7056,7 +7224,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>12</v>
@@ -7067,7 +7235,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>20</v>
@@ -7087,7 +7255,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>20</v>
@@ -7096,12 +7264,12 @@
         <v>17</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>20</v>
@@ -7112,7 +7280,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>26</v>
@@ -7121,12 +7289,12 @@
         <v>17</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>26</v>
@@ -7137,7 +7305,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>28</v>
@@ -7157,7 +7325,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>28</v>
@@ -7177,7 +7345,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>28</v>
@@ -7197,7 +7365,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>28</v>
@@ -7208,7 +7376,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>30</v>
@@ -7228,7 +7396,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>30</v>
@@ -7248,7 +7416,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>30</v>
@@ -7268,7 +7436,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>30</v>
@@ -7277,18 +7445,18 @@
         <v>21</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>30</v>
@@ -7299,7 +7467,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>32</v>
@@ -7319,7 +7487,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>32</v>
@@ -7339,7 +7507,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>32</v>
@@ -7359,7 +7527,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>32</v>
@@ -7370,7 +7538,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>34</v>
@@ -7390,7 +7558,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>34</v>
@@ -7410,7 +7578,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>34</v>
@@ -7430,7 +7598,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>34</v>
@@ -7450,7 +7618,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>34</v>
@@ -7461,7 +7629,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>12</v>
@@ -7481,7 +7649,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>12</v>
@@ -7501,7 +7669,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
@@ -7521,7 +7689,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
@@ -7532,7 +7700,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>20</v>
@@ -7552,7 +7720,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>20</v>
@@ -7561,12 +7729,12 @@
         <v>17</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>20</v>
@@ -7577,7 +7745,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>26</v>
@@ -7586,12 +7754,12 @@
         <v>17</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>26</v>
@@ -7602,7 +7770,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>28</v>
@@ -7622,7 +7790,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>28</v>
@@ -7642,7 +7810,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>28</v>
@@ -7662,7 +7830,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>28</v>
@@ -7673,7 +7841,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>30</v>
@@ -7693,7 +7861,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>30</v>
@@ -7713,7 +7881,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>30</v>
@@ -7733,7 +7901,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>30</v>
@@ -7753,7 +7921,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>30</v>
@@ -7764,7 +7932,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>32</v>
@@ -7784,7 +7952,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>32</v>
@@ -7804,7 +7972,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>32</v>
@@ -7824,7 +7992,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>32</v>
@@ -7835,7 +8003,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>34</v>
@@ -7855,7 +8023,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>34</v>
@@ -7864,12 +8032,12 @@
         <v>17</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>34</v>
@@ -7889,7 +8057,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>34</v>
@@ -7909,7 +8077,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>34</v>
@@ -7920,7 +8088,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>12</v>
@@ -7940,7 +8108,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>12</v>
@@ -7960,7 +8128,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>12</v>
@@ -7980,7 +8148,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>12</v>
@@ -7991,7 +8159,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>20</v>
@@ -8000,12 +8168,12 @@
         <v>17</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>20</v>
@@ -8025,7 +8193,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>20</v>
@@ -8083,7 +8251,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>34</v>
@@ -8092,12 +8260,12 @@
         <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>34</v>
@@ -8108,7 +8276,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -8120,15 +8288,15 @@
         <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
@@ -8140,35 +8308,35 @@
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -8179,7 +8347,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>20</v>
@@ -8199,7 +8367,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
@@ -8208,12 +8376,12 @@
         <v>18</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>20</v>
@@ -8224,7 +8392,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>26</v>
@@ -8233,12 +8401,12 @@
         <v>18</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>26</v>
@@ -8249,7 +8417,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -8269,7 +8437,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
@@ -8289,7 +8457,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -8309,7 +8477,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -8320,7 +8488,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
@@ -8340,7 +8508,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
@@ -8360,7 +8528,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -8380,7 +8548,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -8400,7 +8568,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
@@ -8411,7 +8579,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>32</v>
@@ -8431,7 +8599,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>32</v>
@@ -8451,7 +8619,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>32</v>
@@ -8471,7 +8639,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>32</v>
@@ -8482,7 +8650,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>34</v>
@@ -8502,7 +8670,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>34</v>
@@ -8522,7 +8690,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>34</v>
@@ -8542,7 +8710,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>34</v>
@@ -8554,7 +8722,7 @@
         <v>22</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>46</v>
@@ -8562,7 +8730,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>34</v>
@@ -8573,7 +8741,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
@@ -8593,7 +8761,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -8613,7 +8781,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -8633,7 +8801,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
@@ -8644,7 +8812,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>20</v>
@@ -8664,7 +8832,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>20</v>
@@ -8673,12 +8841,12 @@
         <v>17</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>20</v>
@@ -8689,7 +8857,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>26</v>
@@ -8698,12 +8866,12 @@
         <v>17</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>26</v>
@@ -8714,7 +8882,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -8734,7 +8902,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>28</v>
@@ -8754,7 +8922,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>28</v>
@@ -8765,7 +8933,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
@@ -8785,7 +8953,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -8805,7 +8973,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>30</v>
@@ -8825,7 +8993,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -8836,7 +9004,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>32</v>
@@ -8856,7 +9024,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>32</v>
@@ -8876,7 +9044,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>32</v>
@@ -8887,7 +9055,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>34</v>
@@ -8907,7 +9075,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>34</v>
@@ -8927,7 +9095,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>34</v>
@@ -8942,12 +9110,12 @@
         <v>22</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>34</v>
@@ -8959,7 +9127,7 @@
         <v>22</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>46</v>
@@ -8967,7 +9135,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>34</v>
@@ -8978,7 +9146,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -8998,7 +9166,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
@@ -9018,7 +9186,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>12</v>
@@ -9038,7 +9206,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>12</v>
@@ -9049,7 +9217,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>20</v>
@@ -9069,7 +9237,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>20</v>
@@ -9078,12 +9246,12 @@
         <v>17</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>20</v>
@@ -9094,7 +9262,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>26</v>
@@ -9103,12 +9271,12 @@
         <v>17</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>26</v>
@@ -9119,7 +9287,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -9139,7 +9307,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>28</v>
@@ -9159,7 +9327,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>28</v>
@@ -9170,7 +9338,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>30</v>
@@ -9190,7 +9358,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>30</v>
@@ -9210,7 +9378,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>30</v>
@@ -9230,7 +9398,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>30</v>
@@ -9250,7 +9418,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>30</v>
@@ -9261,7 +9429,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>32</v>
@@ -9273,15 +9441,15 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>32</v>
@@ -9293,15 +9461,15 @@
         <v>14</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>32</v>
@@ -9316,12 +9484,12 @@
         <v>16</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>32</v>
@@ -9332,7 +9500,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>34</v>
@@ -9352,7 +9520,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>34</v>
@@ -9372,7 +9540,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>34</v>
@@ -9392,7 +9560,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>34</v>
@@ -9403,7 +9571,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>12</v>
@@ -9423,7 +9591,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>12</v>
@@ -9443,7 +9611,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -9454,7 +9622,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>20</v>
@@ -9474,7 +9642,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>20</v>
@@ -9485,7 +9653,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>26</v>
@@ -9496,7 +9664,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>28</v>
@@ -9516,7 +9684,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>28</v>
@@ -9536,7 +9704,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -9556,7 +9724,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -9567,7 +9735,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>30</v>
@@ -9587,7 +9755,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>30</v>
@@ -9607,7 +9775,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>30</v>
@@ -9627,7 +9795,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>30</v>
@@ -9647,7 +9815,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>30</v>
@@ -9658,7 +9826,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>32</v>
@@ -9678,7 +9846,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>32</v>
@@ -9698,7 +9866,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>32</v>
@@ -9718,7 +9886,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>32</v>
@@ -9729,7 +9897,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>34</v>
@@ -9749,7 +9917,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>34</v>
@@ -9769,7 +9937,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>34</v>
@@ -9789,7 +9957,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>34</v>
@@ -9809,7 +9977,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>34</v>
@@ -9820,7 +9988,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>12</v>
@@ -9840,7 +10008,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>12</v>
@@ -9860,7 +10028,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>12</v>
@@ -9880,7 +10048,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>12</v>
@@ -9891,7 +10059,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>20</v>
@@ -9900,12 +10068,12 @@
         <v>17</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>20</v>
@@ -9925,7 +10093,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>20</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Databaze Výroba 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="204">
   <si>
     <t>Datum</t>
   </si>
@@ -190,6 +190,33 @@
   </si>
   <si>
     <t>21.05.2026</t>
+  </si>
+  <si>
+    <t>22.05.2026</t>
+  </si>
+  <si>
+    <t>23.05.2026</t>
+  </si>
+  <si>
+    <t>24.05.2026</t>
+  </si>
+  <si>
+    <t>25.05.2026</t>
+  </si>
+  <si>
+    <t>26.05.2026</t>
+  </si>
+  <si>
+    <t>27.05.2026</t>
+  </si>
+  <si>
+    <t>28.05.2026</t>
+  </si>
+  <si>
+    <t>29.05.2026</t>
+  </si>
+  <si>
+    <t>30.05.2026</t>
   </si>
   <si>
     <t>01.04.2026</t>
@@ -2112,6 +2139,445 @@
         <v>41823.0</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H70" s="3">
+        <v>41608.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="3">
+        <v>40928.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H73" s="3">
+        <v>40004.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H76" s="3">
+        <v>40820.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H80" s="3">
+        <v>42140.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H83" s="3">
+        <v>40948.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H87" s="3">
+        <v>41988.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H90" s="3">
+        <v>41143.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H92" s="3">
+        <v>41564.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2161,7 +2627,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>32</v>
@@ -2181,7 +2647,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>32</v>
@@ -2201,7 +2667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>32</v>
@@ -2221,7 +2687,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>32</v>
@@ -2232,7 +2698,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>34</v>
@@ -2252,7 +2718,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>34</v>
@@ -2272,7 +2738,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>34</v>
@@ -2292,7 +2758,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>34</v>
@@ -2312,7 +2778,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>34</v>
@@ -2323,7 +2789,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -2343,7 +2809,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
@@ -2363,7 +2829,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -2383,7 +2849,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -2394,7 +2860,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>20</v>
@@ -2414,7 +2880,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>20</v>
@@ -2425,7 +2891,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>26</v>
@@ -2436,7 +2902,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>28</v>
@@ -2456,7 +2922,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>28</v>
@@ -2476,7 +2942,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>28</v>
@@ -2496,7 +2962,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>28</v>
@@ -2507,7 +2973,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -2527,7 +2993,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>30</v>
@@ -2547,7 +3013,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>30</v>
@@ -2567,13 +3033,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>22</v>
@@ -2582,12 +3048,12 @@
         <v>53</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>30</v>
@@ -2602,12 +3068,12 @@
         <v>23</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>30</v>
@@ -2618,7 +3084,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>32</v>
@@ -2638,7 +3104,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>32</v>
@@ -2658,7 +3124,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>32</v>
@@ -2678,7 +3144,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>32</v>
@@ -2689,7 +3155,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>34</v>
@@ -2709,7 +3175,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>34</v>
@@ -2729,7 +3195,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>34</v>
@@ -2749,7 +3215,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>34</v>
@@ -2769,7 +3235,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>34</v>
@@ -2780,7 +3246,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>12</v>
@@ -2800,7 +3266,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>12</v>
@@ -2820,7 +3286,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>12</v>
@@ -2840,7 +3306,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>12</v>
@@ -2851,7 +3317,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>20</v>
@@ -2871,7 +3337,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>20</v>
@@ -2882,7 +3348,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>26</v>
@@ -2893,7 +3359,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>28</v>
@@ -2913,7 +3379,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>28</v>
@@ -2933,7 +3399,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>28</v>
@@ -2944,7 +3410,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>30</v>
@@ -2964,7 +3430,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>30</v>
@@ -2984,19 +3450,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -3004,7 +3470,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>30</v>
@@ -3013,10 +3479,10 @@
         <v>21</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>14</v>
@@ -3024,7 +3490,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>30</v>
@@ -3035,7 +3501,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>32</v>
@@ -3055,7 +3521,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>32</v>
@@ -3075,7 +3541,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>32</v>
@@ -3095,7 +3561,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>32</v>
@@ -3106,7 +3572,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>34</v>
@@ -3126,7 +3592,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>34</v>
@@ -3146,7 +3612,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>34</v>
@@ -3166,7 +3632,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>34</v>
@@ -3186,7 +3652,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>34</v>
@@ -3197,7 +3663,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>12</v>
@@ -3217,7 +3683,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>12</v>
@@ -3237,7 +3703,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>12</v>
@@ -3248,7 +3714,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>20</v>
@@ -3268,7 +3734,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>20</v>
@@ -3279,7 +3745,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>26</v>
@@ -3290,7 +3756,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>28</v>
@@ -3310,7 +3776,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>28</v>
@@ -3330,7 +3796,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>28</v>
@@ -3341,7 +3807,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>30</v>
@@ -3361,7 +3827,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>30</v>
@@ -3381,19 +3847,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>14</v>
@@ -3401,7 +3867,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>30</v>
@@ -3410,18 +3876,18 @@
         <v>21</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>30</v>
@@ -3432,7 +3898,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>32</v>
@@ -3452,7 +3918,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>32</v>
@@ -3472,7 +3938,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>32</v>
@@ -3483,7 +3949,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>34</v>
@@ -3503,7 +3969,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>34</v>
@@ -3523,7 +3989,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>34</v>
@@ -3543,7 +4009,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>34</v>
@@ -3554,7 +4020,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -3574,7 +4040,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
@@ -3594,7 +4060,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>12</v>
@@ -3605,7 +4071,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>20</v>
@@ -3625,7 +4091,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>20</v>
@@ -3636,7 +4102,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>26</v>
@@ -3647,7 +4113,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -3667,7 +4133,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -3687,7 +4153,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>28</v>
@@ -3698,7 +4164,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>30</v>
@@ -3718,7 +4184,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>30</v>
@@ -3738,27 +4204,27 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>30</v>
@@ -3767,18 +4233,18 @@
         <v>21</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>30</v>
@@ -3789,7 +4255,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>32</v>
@@ -3809,7 +4275,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>32</v>
@@ -3829,7 +4295,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>32</v>
@@ -3840,7 +4306,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>34</v>
@@ -3860,7 +4326,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>34</v>
@@ -3880,7 +4346,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>34</v>
@@ -3900,7 +4366,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>34</v>
@@ -3920,7 +4386,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>34</v>
@@ -3978,7 +4444,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -3987,12 +4453,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>26</v>
@@ -4003,7 +4469,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -4023,7 +4489,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -4043,7 +4509,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>28</v>
@@ -4063,7 +4529,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -4074,7 +4540,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -4094,7 +4560,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
@@ -4114,7 +4580,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -4129,12 +4595,12 @@
         <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>30</v>
@@ -4154,7 +4620,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>30</v>
@@ -4165,7 +4631,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>32</v>
@@ -4185,7 +4651,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>32</v>
@@ -4205,7 +4671,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
@@ -4225,7 +4691,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>32</v>
@@ -4236,7 +4702,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>34</v>
@@ -4256,7 +4722,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>34</v>
@@ -4268,15 +4734,15 @@
         <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>34</v>
@@ -4288,15 +4754,15 @@
         <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>34</v>
@@ -4316,7 +4782,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>34</v>
@@ -4329,12 +4795,12 @@
         <v>40483.5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>34</v>
@@ -4418,7 +4884,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>12</v>
@@ -4438,7 +4904,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>12</v>
@@ -4458,7 +4924,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>12</v>
@@ -4478,7 +4944,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>12</v>
@@ -4489,7 +4955,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>20</v>
@@ -4509,7 +4975,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>20</v>
@@ -4518,12 +4984,12 @@
         <v>17</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>20</v>
@@ -4534,7 +5000,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>26</v>
@@ -4543,12 +5009,12 @@
         <v>17</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>26</v>
@@ -4559,7 +5025,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
@@ -4579,7 +5045,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>28</v>
@@ -4599,7 +5065,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>28</v>
@@ -4619,7 +5085,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>28</v>
@@ -4630,7 +5096,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
@@ -4650,7 +5116,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>30</v>
@@ -4670,7 +5136,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>30</v>
@@ -4690,7 +5156,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>30</v>
@@ -4710,7 +5176,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>30</v>
@@ -4723,12 +5189,12 @@
         <v>41160.0</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>30</v>
@@ -4812,7 +5278,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>32</v>
@@ -4832,7 +5298,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>32</v>
@@ -4852,7 +5318,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>32</v>
@@ -4872,7 +5338,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>32</v>
@@ -4883,7 +5349,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>34</v>
@@ -4903,7 +5369,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>34</v>
@@ -4923,7 +5389,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>34</v>
@@ -4943,7 +5409,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>34</v>
@@ -4963,7 +5429,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>34</v>
@@ -4976,12 +5442,12 @@
         <v>41286.0</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>34</v>
@@ -5065,7 +5531,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>12</v>
@@ -5085,7 +5551,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>12</v>
@@ -5105,7 +5571,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>12</v>
@@ -5125,7 +5591,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -5136,7 +5602,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>20</v>
@@ -5156,7 +5622,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>20</v>
@@ -5165,12 +5631,12 @@
         <v>17</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>20</v>
@@ -5181,7 +5647,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>26</v>
@@ -5190,12 +5656,12 @@
         <v>17</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>26</v>
@@ -5206,7 +5672,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>28</v>
@@ -5226,7 +5692,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>28</v>
@@ -5246,7 +5712,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>28</v>
@@ -5266,7 +5732,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -5277,7 +5743,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>30</v>
@@ -5297,7 +5763,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>30</v>
@@ -5317,7 +5783,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>30</v>
@@ -5337,7 +5803,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>30</v>
@@ -5357,7 +5823,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>30</v>
@@ -5368,7 +5834,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>32</v>
@@ -5388,7 +5854,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>32</v>
@@ -5408,7 +5874,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>32</v>
@@ -5428,7 +5894,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>32</v>
@@ -5441,12 +5907,12 @@
         <v>41264.0</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>32</v>
@@ -5530,7 +5996,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>34</v>
@@ -5550,7 +6016,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>34</v>
@@ -5570,7 +6036,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>34</v>
@@ -5590,7 +6056,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>34</v>
@@ -5601,7 +6067,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>12</v>
@@ -5621,7 +6087,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>12</v>
@@ -5641,7 +6107,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>12</v>
@@ -5661,7 +6127,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -5672,7 +6138,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>20</v>
@@ -5692,7 +6158,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>20</v>
@@ -5701,12 +6167,12 @@
         <v>17</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>20</v>
@@ -5717,7 +6183,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>26</v>
@@ -5726,12 +6192,12 @@
         <v>17</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>26</v>
@@ -5742,7 +6208,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -5762,7 +6228,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -5782,7 +6248,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>28</v>
@@ -5793,7 +6259,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>30</v>
@@ -5813,7 +6279,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>30</v>
@@ -5822,12 +6288,12 @@
         <v>17</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>30</v>
@@ -5847,7 +6313,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>30</v>
@@ -5867,7 +6333,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>30</v>
@@ -5878,7 +6344,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>32</v>
@@ -5898,7 +6364,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>32</v>
@@ -5918,7 +6384,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>32</v>
@@ -5938,7 +6404,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>32</v>
@@ -5949,7 +6415,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>34</v>
@@ -5969,7 +6435,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>34</v>
@@ -5989,7 +6455,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>34</v>
@@ -6009,7 +6475,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>34</v>
@@ -6029,7 +6495,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>34</v>
@@ -6040,7 +6506,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>12</v>
@@ -6060,7 +6526,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>12</v>
@@ -6080,7 +6546,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>12</v>
@@ -6100,7 +6566,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>12</v>
@@ -6111,7 +6577,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>20</v>
@@ -6131,7 +6597,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>20</v>
@@ -6140,12 +6606,12 @@
         <v>17</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>20</v>
@@ -6156,7 +6622,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>26</v>
@@ -6165,12 +6631,12 @@
         <v>17</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>26</v>
@@ -6181,7 +6647,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>28</v>
@@ -6201,7 +6667,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>28</v>
@@ -6221,7 +6687,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>28</v>
@@ -6241,7 +6707,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>28</v>
@@ -6252,7 +6718,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>30</v>
@@ -6272,7 +6738,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>30</v>
@@ -6292,7 +6758,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>30</v>
@@ -6312,19 +6778,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>14</v>
@@ -6332,7 +6798,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>30</v>
@@ -6341,7 +6807,7 @@
         <v>21</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>23</v>
@@ -6352,7 +6818,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>30</v>
@@ -6410,7 +6876,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -6419,12 +6885,12 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>26</v>
@@ -6435,7 +6901,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>28</v>
@@ -6455,7 +6921,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>28</v>
@@ -6475,7 +6941,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>28</v>
@@ -6495,7 +6961,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -6506,7 +6972,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -6518,15 +6984,15 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
@@ -6538,15 +7004,15 @@
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -6558,15 +7024,15 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>30</v>
@@ -6586,7 +7052,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>30</v>
@@ -6597,7 +7063,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>32</v>
@@ -6617,7 +7083,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>32</v>
@@ -6637,7 +7103,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
@@ -6648,7 +7114,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>34</v>
@@ -6668,7 +7134,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>34</v>
@@ -6688,7 +7154,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>34</v>
@@ -6708,7 +7174,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>34</v>
@@ -6719,7 +7185,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -6739,7 +7205,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>12</v>
@@ -6759,7 +7225,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>12</v>
@@ -6779,7 +7245,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>12</v>
@@ -6790,7 +7256,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>20</v>
@@ -6810,7 +7276,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>20</v>
@@ -6819,12 +7285,12 @@
         <v>17</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>20</v>
@@ -6835,7 +7301,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>26</v>
@@ -6844,12 +7310,12 @@
         <v>17</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>26</v>
@@ -6860,7 +7326,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
@@ -6880,7 +7346,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -6900,7 +7366,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -6920,7 +7386,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
@@ -6931,7 +7397,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>30</v>
@@ -6951,7 +7417,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
@@ -6971,7 +7437,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>30</v>
@@ -6991,7 +7457,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
@@ -7011,7 +7477,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>30</v>
@@ -7022,7 +7488,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>32</v>
@@ -7042,7 +7508,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>32</v>
@@ -7062,7 +7528,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>32</v>
@@ -7082,7 +7548,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>32</v>
@@ -7093,7 +7559,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>34</v>
@@ -7105,15 +7571,15 @@
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>34</v>
@@ -7125,15 +7591,15 @@
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>34</v>
@@ -7145,15 +7611,15 @@
         <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>34</v>
@@ -7173,7 +7639,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>34</v>
@@ -7184,7 +7650,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>12</v>
@@ -7204,7 +7670,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>12</v>
@@ -7224,7 +7690,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>12</v>
@@ -7235,7 +7701,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>20</v>
@@ -7255,7 +7721,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>20</v>
@@ -7264,12 +7730,12 @@
         <v>17</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>20</v>
@@ -7280,7 +7746,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>26</v>
@@ -7289,12 +7755,12 @@
         <v>17</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>26</v>
@@ -7305,7 +7771,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>28</v>
@@ -7325,7 +7791,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>28</v>
@@ -7345,7 +7811,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>28</v>
@@ -7365,7 +7831,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>28</v>
@@ -7376,7 +7842,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>30</v>
@@ -7396,7 +7862,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>30</v>
@@ -7416,7 +7882,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>30</v>
@@ -7436,7 +7902,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>30</v>
@@ -7445,18 +7911,18 @@
         <v>21</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>30</v>
@@ -7467,7 +7933,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>32</v>
@@ -7487,7 +7953,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>32</v>
@@ -7507,7 +7973,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>32</v>
@@ -7527,7 +7993,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>32</v>
@@ -7538,7 +8004,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>34</v>
@@ -7558,7 +8024,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>34</v>
@@ -7578,7 +8044,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>34</v>
@@ -7598,7 +8064,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>34</v>
@@ -7618,7 +8084,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>34</v>
@@ -7629,7 +8095,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>12</v>
@@ -7649,7 +8115,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>12</v>
@@ -7669,7 +8135,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
@@ -7689,7 +8155,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
@@ -7700,7 +8166,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>20</v>
@@ -7720,7 +8186,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>20</v>
@@ -7729,12 +8195,12 @@
         <v>17</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>20</v>
@@ -7745,7 +8211,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>26</v>
@@ -7754,12 +8220,12 @@
         <v>17</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>26</v>
@@ -7770,7 +8236,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>28</v>
@@ -7790,7 +8256,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>28</v>
@@ -7810,7 +8276,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>28</v>
@@ -7830,7 +8296,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>28</v>
@@ -7841,7 +8307,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>30</v>
@@ -7861,7 +8327,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>30</v>
@@ -7881,7 +8347,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>30</v>
@@ -7901,7 +8367,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>30</v>
@@ -7921,7 +8387,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>30</v>
@@ -7932,7 +8398,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>32</v>
@@ -7952,7 +8418,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>32</v>
@@ -7972,7 +8438,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>32</v>
@@ -7992,7 +8458,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>32</v>
@@ -8003,7 +8469,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>34</v>
@@ -8023,7 +8489,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>34</v>
@@ -8032,12 +8498,12 @@
         <v>17</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>34</v>
@@ -8057,7 +8523,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>34</v>
@@ -8077,7 +8543,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>34</v>
@@ -8088,7 +8554,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>12</v>
@@ -8108,7 +8574,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>12</v>
@@ -8128,7 +8594,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>12</v>
@@ -8148,7 +8614,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>12</v>
@@ -8159,7 +8625,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>20</v>
@@ -8168,12 +8634,12 @@
         <v>17</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>20</v>
@@ -8193,7 +8659,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>20</v>
@@ -8251,7 +8717,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>34</v>
@@ -8260,12 +8726,12 @@
         <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>34</v>
@@ -8276,7 +8742,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -8288,15 +8754,15 @@
         <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
@@ -8308,35 +8774,35 @@
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -8347,7 +8813,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>20</v>
@@ -8367,7 +8833,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
@@ -8376,12 +8842,12 @@
         <v>18</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>20</v>
@@ -8392,7 +8858,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>26</v>
@@ -8401,12 +8867,12 @@
         <v>18</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>26</v>
@@ -8417,7 +8883,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -8437,7 +8903,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
@@ -8457,7 +8923,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
@@ -8477,7 +8943,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -8488,7 +8954,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>30</v>
@@ -8508,7 +8974,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
@@ -8528,7 +8994,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>30</v>
@@ -8548,7 +9014,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -8568,7 +9034,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>30</v>
@@ -8579,7 +9045,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>32</v>
@@ -8599,7 +9065,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>32</v>
@@ -8619,7 +9085,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>32</v>
@@ -8639,7 +9105,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>32</v>
@@ -8650,7 +9116,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>34</v>
@@ -8670,7 +9136,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>34</v>
@@ -8690,7 +9156,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>34</v>
@@ -8710,7 +9176,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>34</v>
@@ -8722,7 +9188,7 @@
         <v>22</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>46</v>
@@ -8730,7 +9196,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>34</v>
@@ -8741,7 +9207,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
@@ -8761,7 +9227,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
@@ -8781,7 +9247,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -8801,7 +9267,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
@@ -8812,7 +9278,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>20</v>
@@ -8832,7 +9298,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>20</v>
@@ -8841,12 +9307,12 @@
         <v>17</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>20</v>
@@ -8857,7 +9323,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>26</v>
@@ -8866,12 +9332,12 @@
         <v>17</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>26</v>
@@ -8882,7 +9348,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -8902,7 +9368,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>28</v>
@@ -8922,7 +9388,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>28</v>
@@ -8933,7 +9399,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>30</v>
@@ -8953,7 +9419,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -8973,7 +9439,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>30</v>
@@ -8993,7 +9459,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>30</v>
@@ -9004,7 +9470,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>32</v>
@@ -9024,7 +9490,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>32</v>
@@ -9044,7 +9510,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>32</v>
@@ -9055,7 +9521,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>34</v>
@@ -9075,7 +9541,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>34</v>
@@ -9095,7 +9561,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>34</v>
@@ -9110,12 +9576,12 @@
         <v>22</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>34</v>
@@ -9127,7 +9593,7 @@
         <v>22</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>46</v>
@@ -9135,7 +9601,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>34</v>
@@ -9146,7 +9612,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
@@ -9166,7 +9632,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
@@ -9186,7 +9652,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>12</v>
@@ -9206,7 +9672,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>12</v>
@@ -9217,7 +9683,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>20</v>
@@ -9237,7 +9703,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>20</v>
@@ -9246,12 +9712,12 @@
         <v>17</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>20</v>
@@ -9262,7 +9728,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>26</v>
@@ -9271,12 +9737,12 @@
         <v>17</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>26</v>
@@ -9287,7 +9753,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>28</v>
@@ -9307,7 +9773,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>28</v>
@@ -9327,7 +9793,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>28</v>
@@ -9338,7 +9804,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>30</v>
@@ -9358,7 +9824,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>30</v>
@@ -9378,7 +9844,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>30</v>
@@ -9398,7 +9864,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>30</v>
@@ -9418,7 +9884,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>30</v>
@@ -9429,7 +9895,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>32</v>
@@ -9441,15 +9907,15 @@
         <v>14</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>32</v>
@@ -9461,15 +9927,15 @@
         <v>14</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>32</v>
@@ -9484,12 +9950,12 @@
         <v>16</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>32</v>
@@ -9500,7 +9966,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>34</v>
@@ -9520,7 +9986,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>34</v>
@@ -9540,7 +10006,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>34</v>
@@ -9560,7 +10026,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>34</v>
@@ -9571,7 +10037,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>12</v>
@@ -9591,7 +10057,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>12</v>
@@ -9611,7 +10077,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -9622,7 +10088,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>20</v>
@@ -9642,7 +10108,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>20</v>
@@ -9653,7 +10119,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>26</v>
@@ -9664,7 +10130,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>28</v>
@@ -9684,7 +10150,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>28</v>
@@ -9704,7 +10170,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>28</v>
@@ -9724,7 +10190,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>28</v>
@@ -9735,7 +10201,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>30</v>
@@ -9755,7 +10221,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>30</v>
@@ -9775,7 +10241,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>30</v>
@@ -9795,7 +10261,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>30</v>
@@ -9815,7 +10281,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>30</v>
@@ -9826,7 +10292,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>32</v>
@@ -9846,7 +10312,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>32</v>
@@ -9866,7 +10332,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>32</v>
@@ -9886,7 +10352,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>32</v>
@@ -9897,7 +10363,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>34</v>
@@ -9917,7 +10383,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>34</v>
@@ -9937,7 +10403,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>34</v>
@@ -9957,7 +10423,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>34</v>
@@ -9977,7 +10443,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>34</v>
@@ -9988,7 +10454,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>12</v>
@@ -10008,7 +10474,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>12</v>
@@ -10028,7 +10494,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>12</v>
@@ -10048,7 +10514,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>12</v>
@@ -10059,7 +10525,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>20</v>
@@ -10068,12 +10534,12 @@
         <v>17</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>20</v>
@@ -10093,7 +10559,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>20</v>
